--- a/students.xlsx
+++ b/students.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C535"/>
+  <dimension ref="A1:C552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>나주비</t>
+          <t>박현서</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>334</t>
         </is>
       </c>
     </row>
@@ -458,12 +458,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>김나현</t>
+          <t>김세민</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>317</t>
         </is>
       </c>
     </row>
@@ -475,12 +475,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>김예나</t>
+          <t>김윤태</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>325</t>
         </is>
       </c>
     </row>
@@ -492,12 +492,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>이혜성</t>
+          <t>최해민</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>407</t>
         </is>
       </c>
     </row>
@@ -509,12 +509,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>정현지</t>
+          <t>최우진</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>377</t>
         </is>
       </c>
     </row>
@@ -526,12 +526,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>조윤영</t>
+          <t>채윤기</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>398</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>문지현</t>
+          <t>김유찬</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>351</t>
         </is>
       </c>
     </row>
@@ -560,12 +560,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>부채영</t>
+          <t>박소윤</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>228</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>함지성</t>
+          <t>한보미</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>157</t>
         </is>
       </c>
     </row>
@@ -594,12 +594,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>이승혜</t>
+          <t>오주영</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>231</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>정윤지</t>
+          <t>심지호</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>321</t>
         </is>
       </c>
     </row>
@@ -628,12 +628,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>김희은</t>
+          <t>엄창통</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>362</t>
         </is>
       </c>
     </row>
@@ -645,12 +645,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>이채연</t>
+          <t>이건명</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>302</t>
         </is>
       </c>
     </row>
@@ -662,12 +662,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>함재원</t>
+          <t>조성재</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>362</t>
         </is>
       </c>
     </row>
@@ -679,12 +679,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>이하영</t>
+          <t>주하선</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>384</t>
         </is>
       </c>
     </row>
@@ -696,12 +696,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>김나영</t>
+          <t>강기훈</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>369</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>김희서</t>
+          <t>나민솔</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>132</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>김효빈</t>
+          <t>김태이</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>188</t>
         </is>
       </c>
     </row>
@@ -747,12 +747,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>고희원</t>
+          <t>김하영</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>159</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>차소윤</t>
+          <t>최지유</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>202</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>배수민</t>
+          <t>박세린</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>박서현</t>
+          <t>김채현</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>145</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>임유이</t>
+          <t>이서인</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>161</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>윤지우</t>
+          <t>이재희</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>이수빈</t>
+          <t>이지우B</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>148</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>박나리</t>
+          <t>김지율</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>333</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>안신영</t>
+          <t>문예서</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>205</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>정혜원</t>
+          <t>정햇살</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>135</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>김서영</t>
+          <t>김은지</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>172</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>강재원</t>
+          <t>강민재</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>342</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>강지윤</t>
+          <t>김시영</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>329</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>제예원</t>
+          <t>홍동기</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>383</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>김도연</t>
+          <t>김수연</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>141</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>조유나</t>
+          <t>탁윈</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>329</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>이서연</t>
+          <t>이예승</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>371</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>최효원</t>
+          <t>홍승준</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>361</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>신서빈</t>
+          <t>송민우</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>355</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>심진명</t>
+          <t>백준하</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>406</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>권도연</t>
+          <t>김대임</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>230</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>전하윤</t>
+          <t>채윤우</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>373</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>이하정</t>
+          <t>정대현</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>328</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>이지윤</t>
+          <t>이지호</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>195</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>유채연</t>
+          <t>오한별</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>410</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>김지민</t>
+          <t>문채윤</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>201</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>이선주</t>
+          <t>장윤우</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>306</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>황지원</t>
+          <t>황진서</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>139</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>이명은</t>
+          <t>이종준</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>349</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>김은서</t>
+          <t>김명현</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>143</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>신배원</t>
+          <t>유현우</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>297</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>김서연</t>
+          <t>민서현</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>193</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>방서현</t>
+          <t>김진서</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>148</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>모서진</t>
+          <t>박준영</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>327</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>김가율</t>
+          <t>김민준</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>337</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>김서정</t>
+          <t>강재원</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>168</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>김현지</t>
+          <t>박단비</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>128</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>양연지</t>
+          <t>이효주</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>문채윤</t>
+          <t>박지호</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>328</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>이유나</t>
+          <t>이유은</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>김연서</t>
+          <t>김지수</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>324</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>김여진</t>
+          <t>방서현</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>215</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>김채현</t>
+          <t>나정희</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>388</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>류다원</t>
+          <t>박창서</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>411</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>윤영서</t>
+          <t>윤서현</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>172</t>
         </is>
       </c>
     </row>
@@ -1665,12 +1665,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>김주원</t>
+          <t>김조윤</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>224</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>이초민</t>
+          <t>임진영</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>356</t>
         </is>
       </c>
     </row>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>이지아</t>
+          <t>이시연</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>159</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>윤하온</t>
+          <t>송주헌</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>298</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>이효윤</t>
+          <t>정윤지</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>162</t>
         </is>
       </c>
     </row>
@@ -1767,12 +1767,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>김시아</t>
+          <t>고희원</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>179</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>송은서</t>
+          <t>오정환</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>343</t>
         </is>
       </c>
     </row>
@@ -1801,12 +1801,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>김향지</t>
+          <t>박소희</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>224</t>
         </is>
       </c>
     </row>
@@ -1818,12 +1818,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>신지우</t>
+          <t>서승원</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>358</t>
         </is>
       </c>
     </row>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>이현서</t>
+          <t>정선우</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>182</t>
         </is>
       </c>
     </row>
@@ -1852,12 +1852,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>조은호</t>
+          <t>최현태</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>325</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>이효선</t>
+          <t>정유민</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -1886,12 +1886,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>어은재</t>
+          <t>박나리</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>151</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>정지윤</t>
+          <t>진현유</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>150</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>김아라</t>
+          <t>박연희</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>190</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>이시연</t>
+          <t>이정윤</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>233</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1954,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>강태연</t>
+          <t>김성윤</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>411</t>
         </is>
       </c>
     </row>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>이정윤</t>
+          <t>윤성원</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>301</t>
         </is>
       </c>
     </row>
@@ -1988,12 +1988,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>박윤하</t>
+          <t>양윤진</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>178</t>
         </is>
       </c>
     </row>
@@ -2005,12 +2005,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>엄지은</t>
+          <t>손다나</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>160</t>
         </is>
       </c>
     </row>
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>장은재</t>
+          <t>이태욱</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>303</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>양채원</t>
+          <t>전지인</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>187</t>
         </is>
       </c>
     </row>
@@ -2056,12 +2056,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>김소은</t>
+          <t>김준희</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>386</t>
         </is>
       </c>
     </row>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>신찬이</t>
+          <t>김지호</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>주서현</t>
+          <t>허제</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>313</t>
         </is>
       </c>
     </row>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>김아현</t>
+          <t>박주혁</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>384</t>
         </is>
       </c>
     </row>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>이지안</t>
+          <t>배수민</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>152</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>권지민</t>
+          <t>김가율</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>186</t>
         </is>
       </c>
     </row>
@@ -2158,12 +2158,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>김희은</t>
+          <t>나동민</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>402</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>이지우B</t>
+          <t>조민준</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>307</t>
         </is>
       </c>
     </row>
@@ -2192,12 +2192,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>최하랑</t>
+          <t>최현석</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>357</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>전율리</t>
+          <t>정연빈</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>299</t>
         </is>
       </c>
     </row>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>유일서</t>
+          <t>심진명</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>227</t>
         </is>
       </c>
     </row>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>안지운</t>
+          <t>이정연</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>391</t>
         </is>
       </c>
     </row>
@@ -2260,12 +2260,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>서효령</t>
+          <t>김상우</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>377</t>
         </is>
       </c>
     </row>
@@ -2277,12 +2277,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>김예주</t>
+          <t>김소은</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>142</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>나하연</t>
+          <t>노수아</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>201</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>염유진</t>
+          <t>이승원</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>315</t>
         </is>
       </c>
     </row>
@@ -2345,12 +2345,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>장진명</t>
+          <t>장서현</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>373</t>
         </is>
       </c>
     </row>
@@ -2362,12 +2362,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>송주하</t>
+          <t>배서준</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>405</t>
         </is>
       </c>
     </row>
@@ -2379,12 +2379,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>김리나</t>
+          <t>류다원</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>133</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>강연지</t>
+          <t>고현준</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>409</t>
         </is>
       </c>
     </row>
@@ -2413,12 +2413,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>유지민</t>
+          <t>신서안</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>409</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2430,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>김린하</t>
+          <t>김주원</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>127</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>곽수현</t>
+          <t>김경호</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>365</t>
         </is>
       </c>
     </row>
@@ -2464,12 +2464,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>문예서</t>
+          <t>송강민</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>323</t>
         </is>
       </c>
     </row>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>이유빈</t>
+          <t>윤해린</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -2498,12 +2498,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>우지원</t>
+          <t>이우진</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>367</t>
         </is>
       </c>
     </row>
@@ -2515,12 +2515,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>이채원</t>
+          <t>정다경</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>217</t>
         </is>
       </c>
     </row>
@@ -2532,12 +2532,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>박희주</t>
+          <t>이다윤</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>198</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>이도하</t>
+          <t>윤태규</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>367</t>
         </is>
       </c>
     </row>
@@ -2566,12 +2566,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>송서영</t>
+          <t>이은혁</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>394</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>주수빈</t>
+          <t>조동건</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>309</t>
         </is>
       </c>
     </row>
@@ -2600,12 +2600,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>김규리</t>
+          <t>김서영</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>137</t>
         </is>
       </c>
     </row>
@@ -2617,12 +2617,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>박규민</t>
+          <t>김민섭</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>344</t>
         </is>
       </c>
     </row>
@@ -2634,12 +2634,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>박서아</t>
+          <t>유예원</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>204</t>
         </is>
       </c>
     </row>
@@ -2651,12 +2651,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>박소윤</t>
+          <t>김서원</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>144</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>정예원</t>
+          <t>조무빈</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>316</t>
         </is>
       </c>
     </row>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>양채희</t>
+          <t>전현지</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>120</t>
         </is>
       </c>
     </row>
@@ -2702,12 +2702,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>백희원</t>
+          <t>김희서</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>148</t>
         </is>
       </c>
     </row>
@@ -2719,12 +2719,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>이서준B</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>338</t>
         </is>
       </c>
     </row>
@@ -2736,12 +2736,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>이소희</t>
+          <t>박소윤</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>178</t>
         </is>
       </c>
     </row>
@@ -2753,12 +2753,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>김지윤</t>
+          <t>박재성</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>358</t>
         </is>
       </c>
     </row>
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>김지호</t>
+          <t>오현소</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>133</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>유하진</t>
+          <t>이창민</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>314</t>
         </is>
       </c>
     </row>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>조윤서</t>
+          <t>유하진</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>155</t>
         </is>
       </c>
     </row>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>이지민</t>
+          <t>정가을</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>303</t>
         </is>
       </c>
     </row>
@@ -2838,12 +2838,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>이예진</t>
+          <t>전선우</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>216</t>
         </is>
       </c>
     </row>
@@ -2872,12 +2872,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>이수민</t>
+          <t>정재훈</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>389</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>유아림</t>
+          <t>이수진</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>207</t>
         </is>
       </c>
     </row>
@@ -2906,12 +2906,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>이재희</t>
+          <t>이채원</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>192</t>
         </is>
       </c>
     </row>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>이은초</t>
+          <t>이지한B</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>385</t>
         </is>
       </c>
     </row>
@@ -2940,12 +2940,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>이해온</t>
+          <t>윤지우</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>152</t>
         </is>
       </c>
     </row>
@@ -2957,12 +2957,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>이수진</t>
+          <t>이하진</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>394</t>
         </is>
       </c>
     </row>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>전혜린</t>
+          <t>주수빈</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>187</t>
         </is>
       </c>
     </row>
@@ -2991,12 +2991,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>송유경</t>
+          <t>이성준</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>334</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>박연희</t>
+          <t>신수빈</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -3025,12 +3025,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>유다혜</t>
+          <t>이지원A</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>213</t>
         </is>
       </c>
     </row>
@@ -3042,12 +3042,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>권민서</t>
+          <t>김주하</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>131</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>설다혜</t>
+          <t>윤태영</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>360</t>
         </is>
       </c>
     </row>
@@ -3076,12 +3076,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>최다인</t>
+          <t>정보민</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>172</t>
         </is>
       </c>
     </row>
@@ -3093,12 +3093,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>김연우</t>
+          <t>김성관</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>379</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>전지인</t>
+          <t>정희선</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>234</t>
         </is>
       </c>
     </row>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>윤다인</t>
+          <t>이준우</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>405</t>
         </is>
       </c>
     </row>
@@ -3144,12 +3144,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>황유진</t>
+          <t>한지오</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>400</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>김세빈</t>
+          <t>권도연</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>206</t>
         </is>
       </c>
     </row>
@@ -3178,12 +3178,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>권근아</t>
+          <t>공지윤</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>158</t>
         </is>
       </c>
     </row>
@@ -3195,12 +3195,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>황라희</t>
+          <t>황준하</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>403</t>
         </is>
       </c>
     </row>
@@ -3212,12 +3212,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>김주하</t>
+          <t>김민지</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>156</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>박채은A</t>
+          <t>신호진</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>392</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>이지호</t>
+          <t>조현승</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>397</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3263,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>윤담희</t>
+          <t>이은채</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>135</t>
         </is>
       </c>
     </row>
@@ -3280,12 +3280,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>조보민</t>
+          <t>조은호</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>116</t>
         </is>
       </c>
     </row>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>이진서A</t>
+          <t>최수헌</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>160</t>
         </is>
       </c>
     </row>
@@ -3314,12 +3314,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>이미소</t>
+          <t>이소희</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>192</t>
         </is>
       </c>
     </row>
@@ -3331,12 +3331,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>박소희</t>
+          <t>김형은</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>350</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>민서현</t>
+          <t>서유진</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>169</t>
         </is>
       </c>
     </row>
@@ -3382,12 +3382,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>서주은</t>
+          <t>박승빈</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>354</t>
         </is>
       </c>
     </row>
@@ -3399,12 +3399,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>정유민</t>
+          <t>최예훈</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>363</t>
         </is>
       </c>
     </row>
@@ -3416,12 +3416,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>노혜령</t>
+          <t>염유진</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>191</t>
         </is>
       </c>
     </row>
@@ -3433,12 +3433,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>박다현</t>
+          <t>이명은</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>145</t>
         </is>
       </c>
     </row>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>곽다은</t>
+          <t>권민서</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>158</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>양희우</t>
+          <t>신지민</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>140</t>
         </is>
       </c>
     </row>
@@ -3484,12 +3484,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>유예원</t>
+          <t>이가영</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>132</t>
         </is>
       </c>
     </row>
@@ -3501,12 +3501,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>황유정</t>
+          <t>황지원</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>134</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>여은수</t>
+          <t>원태경</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>360</t>
         </is>
       </c>
     </row>
@@ -3535,12 +3535,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>이시아</t>
+          <t>이지민</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>189</t>
         </is>
       </c>
     </row>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>이가영</t>
+          <t>윤지환</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>361</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>이지인</t>
+          <t>이창휘</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>363</t>
         </is>
       </c>
     </row>
@@ -3586,12 +3586,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>김은지</t>
+          <t>류다연</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>126</t>
         </is>
       </c>
     </row>
@@ -3603,12 +3603,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>김현수</t>
+          <t>김대윤</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>396</t>
         </is>
       </c>
     </row>
@@ -3620,12 +3620,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>김채현</t>
+          <t>박서준</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>382</t>
         </is>
       </c>
     </row>
@@ -3637,12 +3637,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>류서연</t>
+          <t>박선하</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>164</t>
         </is>
       </c>
     </row>
@@ -3654,12 +3654,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>김태인</t>
+          <t>모서진</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>138</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>박소연</t>
+          <t>윤지우</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>153</t>
         </is>
       </c>
     </row>
@@ -3705,12 +3705,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>문민서</t>
+          <t>박신휴</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>385</t>
         </is>
       </c>
     </row>
@@ -3722,12 +3722,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>박서연</t>
+          <t>박지유</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>184</t>
         </is>
       </c>
     </row>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>유시연</t>
+          <t>이유정</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>183</t>
         </is>
       </c>
     </row>
@@ -3756,12 +3756,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>이다윤</t>
+          <t>임유이</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>210</t>
         </is>
       </c>
     </row>
@@ -3773,12 +3773,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>구지후</t>
+          <t>김언약</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>353</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>박채은B</t>
+          <t>유준서</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>313</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>이지우A</t>
+          <t>정다은</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>139</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>한은재</t>
+          <t>한수웅</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>383</t>
         </is>
       </c>
     </row>
@@ -3841,12 +3841,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>박단비</t>
+          <t>신예주</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>174</t>
         </is>
       </c>
     </row>
@@ -3858,12 +3858,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>이하연</t>
+          <t>임지원</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>143</t>
         </is>
       </c>
     </row>
@@ -3875,12 +3875,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>진현유</t>
+          <t>조원혁</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>318</t>
         </is>
       </c>
     </row>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>선한빛</t>
+          <t>김영도</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>372</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3909,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>한준희</t>
+          <t>현새한</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>322</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>김효은</t>
+          <t>송지호</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>395</t>
         </is>
       </c>
     </row>
@@ -3943,12 +3943,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>손다나</t>
+          <t>이다연</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -3960,12 +3960,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>박주영</t>
+          <t>신배원</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>208</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>김대임</t>
+          <t>권시윤</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>220</t>
         </is>
       </c>
     </row>
@@ -3994,12 +3994,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>김재인</t>
+          <t>문선아</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>146</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>박지유</t>
+          <t>김호은</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>225</t>
         </is>
       </c>
     </row>
@@ -4028,12 +4028,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>이서윤B</t>
+          <t>장은재</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -4045,12 +4045,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>서지우</t>
+          <t>이서윤B</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>127</t>
         </is>
       </c>
     </row>
@@ -4062,12 +4062,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>정희선</t>
+          <t>전윤형</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>205</t>
         </is>
       </c>
     </row>
@@ -4079,12 +4079,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>최하윤</t>
+          <t>최호란</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>168</t>
         </is>
       </c>
     </row>
@@ -4096,12 +4096,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>김수연</t>
+          <t>김윤찬</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>324</t>
         </is>
       </c>
     </row>
@@ -4113,12 +4113,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>나민솔</t>
+          <t>김원중</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>305</t>
         </is>
       </c>
     </row>
@@ -4130,12 +4130,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>최린아</t>
+          <t>하윤채</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>144</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>김효주</t>
+          <t>김연우</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>144</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>박지우</t>
+          <t>어은재</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>123</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>최세영</t>
+          <t>주창휘</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>400</t>
         </is>
       </c>
     </row>
@@ -4198,12 +4198,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>이승희</t>
+          <t>정지윤</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>156</t>
         </is>
       </c>
     </row>
@@ -4215,12 +4215,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>신수빈</t>
+          <t>배선우</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>229</t>
         </is>
       </c>
     </row>
@@ -4232,12 +4232,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>정하늬</t>
+          <t>제예원</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>124</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>전지은</t>
+          <t>조광현</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -4266,12 +4266,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>강유민</t>
+          <t>곽수현</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>209</t>
         </is>
       </c>
     </row>
@@ -4283,12 +4283,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>김희서</t>
+          <t>김하린</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>199</t>
         </is>
       </c>
     </row>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>박혜정</t>
+          <t>안준성</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>344</t>
         </is>
       </c>
     </row>
@@ -4317,12 +4317,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>신지윤</t>
+          <t>배지우</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>117</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>황주원</t>
+          <t>한채민</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>194</t>
         </is>
       </c>
     </row>
@@ -4351,12 +4351,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>김하영</t>
+          <t>허태영</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>194</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>정선우</t>
+          <t>최세영</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>218</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>김은재</t>
+          <t>김효주</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>196</t>
         </is>
       </c>
     </row>
@@ -4402,12 +4402,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>윤정원</t>
+          <t>윤준우</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>307</t>
         </is>
       </c>
     </row>
@@ -4419,12 +4419,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>양윤진</t>
+          <t>양희우</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>235</t>
         </is>
       </c>
     </row>
@@ -4436,12 +4436,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>김수민</t>
+          <t>김승원</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>312</t>
         </is>
       </c>
     </row>
@@ -4453,12 +4453,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>길현서</t>
+          <t>고준우</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>341</t>
         </is>
       </c>
     </row>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>조정연</t>
+          <t>차재혁</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>314</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>최서윤</t>
+          <t>한준희</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>222</t>
         </is>
       </c>
     </row>
@@ -4504,12 +4504,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>이서아</t>
+          <t>윤장원</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>330</t>
         </is>
       </c>
     </row>
@@ -4521,12 +4521,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>이은채</t>
+          <t>이도연</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>308</t>
         </is>
       </c>
     </row>
@@ -4538,12 +4538,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>박정유</t>
+          <t>김린하</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>166</t>
         </is>
       </c>
     </row>
@@ -4555,12 +4555,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>김호은</t>
+          <t>문하은</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -4572,12 +4572,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>김지나</t>
+          <t>송민종</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>354</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>윤은빈</t>
+          <t>이현진</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>315</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>이채린</t>
+          <t>이희우</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>136</t>
         </is>
       </c>
     </row>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>정다은</t>
+          <t>정지윤</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>134</t>
         </is>
       </c>
     </row>
@@ -4640,12 +4640,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>엄주은</t>
+          <t>백희원</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>151</t>
         </is>
       </c>
     </row>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>이승채</t>
+          <t>장하렴</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>215</t>
         </is>
       </c>
     </row>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>김소래</t>
+          <t>김태환</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>351</t>
         </is>
       </c>
     </row>
@@ -4691,12 +4691,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>박진아</t>
+          <t>김서율</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>145</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4708,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>김아빈</t>
+          <t>김규연</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>153</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>박세아</t>
+          <t>송유경</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>135</t>
         </is>
       </c>
     </row>
@@ -4759,12 +4759,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>서지호</t>
+          <t>방기윤</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>345</t>
         </is>
       </c>
     </row>
@@ -4776,12 +4776,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>이루미</t>
+          <t>신이수</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>150</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>이진서B</t>
+          <t>이지한A</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>408</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>장지후</t>
+          <t>이수빈</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>162</t>
         </is>
       </c>
     </row>
@@ -4844,12 +4844,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>김선희</t>
+          <t>김서연</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>155</t>
         </is>
       </c>
     </row>
@@ -4861,12 +4861,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>전지원</t>
+          <t>이유현</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>348</t>
         </is>
       </c>
     </row>
@@ -4878,12 +4878,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>김경현</t>
+          <t>김서정</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -4895,12 +4895,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>형태은</t>
+          <t>황규태</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>323</t>
         </is>
       </c>
     </row>
@@ -4912,12 +4912,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>오현소</t>
+          <t>유다연</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>166</t>
         </is>
       </c>
     </row>
@@ -4929,12 +4929,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>윤해린</t>
+          <t>이루미</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>143</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>이은서</t>
+          <t>이준익</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>343</t>
         </is>
       </c>
     </row>
@@ -4963,12 +4963,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>김효신</t>
+          <t>서지호</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>198</t>
         </is>
       </c>
     </row>
@@ -4980,12 +4980,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>임지원</t>
+          <t>전지원</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>190</t>
         </is>
       </c>
     </row>
@@ -4997,12 +4997,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>이희우</t>
+          <t>이준호</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>346</t>
         </is>
       </c>
     </row>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>김재인</t>
+          <t>김희은</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>173</t>
         </is>
       </c>
     </row>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>김혜연</t>
+          <t>박진아</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>185</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>전현지</t>
+          <t>차지석</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>353</t>
         </is>
       </c>
     </row>
@@ -5065,12 +5065,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>윤서현</t>
+          <t>이승혜</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>165</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>이은혁</t>
+          <t>정진영</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>301</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>권민석</t>
+          <t>권율리</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>171</t>
         </is>
       </c>
     </row>
@@ -5116,12 +5116,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>김진호</t>
+          <t>김형준</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>407</t>
         </is>
       </c>
     </row>
@@ -5133,12 +5133,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>이정연</t>
+          <t>장도훈</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>372</t>
         </is>
       </c>
     </row>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>백한솔</t>
+          <t>송주하</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>142</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>이지한A</t>
+          <t>장지욱</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>319</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>장지욱</t>
+          <t>조은솔</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>120</t>
         </is>
       </c>
     </row>
@@ -5201,12 +5201,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>오정환</t>
+          <t>유다혜</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>129</t>
         </is>
       </c>
     </row>
@@ -5218,12 +5218,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>이기영</t>
+          <t>이서준A</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>339</t>
         </is>
       </c>
     </row>
@@ -5235,12 +5235,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>이우진</t>
+          <t>이예진</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>203</t>
         </is>
       </c>
     </row>
@@ -5252,12 +5252,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>정진영</t>
+          <t>조희재</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>167</t>
         </is>
       </c>
     </row>
@@ -5269,12 +5269,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>장지욱</t>
+          <t>부채영</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>216</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>함석진</t>
+          <t>홍정혁</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>382</t>
         </is>
       </c>
     </row>
@@ -5303,12 +5303,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>김용호</t>
+          <t>박시원</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>370</t>
         </is>
       </c>
     </row>
@@ -5320,12 +5320,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>김태훈</t>
+          <t>백한솔</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>349</t>
         </is>
       </c>
     </row>
@@ -5337,12 +5337,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>이성준</t>
+          <t>안연수</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>299</t>
         </is>
       </c>
     </row>
@@ -5354,12 +5354,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>이예승</t>
+          <t>유예슬</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>232</t>
         </is>
       </c>
     </row>
@@ -5371,12 +5371,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>이진율</t>
+          <t>장하현</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>366</t>
         </is>
       </c>
     </row>
@@ -5388,12 +5388,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>오영웅</t>
+          <t>서인성</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>408</t>
         </is>
       </c>
     </row>
@@ -5405,12 +5405,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>강현우</t>
+          <t>김재인</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>219</t>
         </is>
       </c>
     </row>
@@ -5422,12 +5422,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>유도영</t>
+          <t>유아림</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>171</t>
         </is>
       </c>
     </row>
@@ -5439,12 +5439,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>유현우</t>
+          <t>윤서준</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>306</t>
         </is>
       </c>
     </row>
@@ -5456,12 +5456,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>최세진</t>
+          <t>최승호</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>357</t>
         </is>
       </c>
     </row>
@@ -5473,12 +5473,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>이종준</t>
+          <t>이하율</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>128</t>
         </is>
       </c>
     </row>
@@ -5490,12 +5490,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>장도훈</t>
+          <t>임채린</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>129</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>최인태</t>
+          <t>함수린</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>141</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>주하선</t>
+          <t>최서진</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>136</t>
         </is>
       </c>
     </row>
@@ -5558,12 +5558,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>이지수</t>
+          <t>유시우</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>347</t>
         </is>
       </c>
     </row>
@@ -5609,12 +5609,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>정가을</t>
+          <t>이윤지</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -5626,12 +5626,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>이현준</t>
+          <t>조윤서</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>197</t>
         </is>
       </c>
     </row>
@@ -5643,12 +5643,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>이주영</t>
+          <t>정희도</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>336</t>
         </is>
       </c>
     </row>
@@ -5660,12 +5660,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>유준우</t>
+          <t>이윤석</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>355</t>
         </is>
       </c>
     </row>
@@ -5677,12 +5677,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>김범진</t>
+          <t>김재인</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>131</t>
         </is>
       </c>
     </row>
@@ -5694,12 +5694,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>장서현</t>
+          <t>배정훈</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>312</t>
         </is>
       </c>
     </row>
@@ -5711,12 +5711,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>김재윤</t>
+          <t>기정훈</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>362</t>
         </is>
       </c>
     </row>
@@ -5728,12 +5728,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>엄윤재</t>
+          <t>정인성</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>345</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>최은호</t>
+          <t>최주영</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>300</t>
         </is>
       </c>
     </row>
@@ -5762,12 +5762,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>이찬형</t>
+          <t>최은호</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>337</t>
         </is>
       </c>
     </row>
@@ -5779,12 +5779,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>조영인</t>
+          <t>조인서</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>164</t>
         </is>
       </c>
     </row>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>오윤석</t>
+          <t>이영진</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>381</t>
         </is>
       </c>
     </row>
@@ -5813,12 +5813,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>신민우</t>
+          <t>윤지호</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>345</t>
         </is>
       </c>
     </row>
@@ -5830,12 +5830,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>최이환</t>
+          <t>최하랑</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>정연빈</t>
+          <t>임단우</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>357</t>
         </is>
       </c>
     </row>
@@ -5864,12 +5864,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>차재혁</t>
+          <t>장하준</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>363</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>강지훈</t>
+          <t>권근아</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>213</t>
         </is>
       </c>
     </row>
@@ -5898,12 +5898,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>김규헌</t>
+          <t>김현지</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>140</t>
         </is>
       </c>
     </row>
@@ -5915,12 +5915,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>김지수</t>
+          <t>김선진</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>신준환</t>
+          <t>이은서</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>147</t>
         </is>
       </c>
     </row>
@@ -5949,12 +5949,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>임서준</t>
+          <t>정혜원</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>220</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>신정욱</t>
+          <t>신민수</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>356</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>김성윤</t>
+          <t>박채은A</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>114</t>
         </is>
       </c>
     </row>
@@ -6000,12 +6000,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>김모세</t>
+          <t>강지윤</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>122</t>
         </is>
       </c>
     </row>
@@ -6017,12 +6017,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>김준영</t>
+          <t>박규연</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>147</t>
         </is>
       </c>
     </row>
@@ -6034,12 +6034,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>곽민기</t>
+          <t>김나현</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>188</t>
         </is>
       </c>
     </row>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>장지우</t>
+          <t>이현지</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>197</t>
         </is>
       </c>
     </row>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>이영진</t>
+          <t>이시현</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>375</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>곽환준</t>
+          <t>김재윤</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>330</t>
         </is>
       </c>
     </row>
@@ -6102,12 +6102,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>이예준</t>
+          <t>이하영</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>169</t>
         </is>
       </c>
     </row>
@@ -6119,12 +6119,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>구승규</t>
+          <t>김민성</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>318</t>
         </is>
       </c>
     </row>
@@ -6136,12 +6136,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>김우성</t>
+          <t>김효신</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>174</t>
         </is>
       </c>
     </row>
@@ -6153,12 +6153,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>임동우</t>
+          <t>임하은</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>204</t>
         </is>
       </c>
     </row>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>변윤성</t>
+          <t>이수민</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>161</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>나정희</t>
+          <t>박선유</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>154</t>
         </is>
       </c>
     </row>
@@ -6204,12 +6204,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>류우섭</t>
+          <t>신민우</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>386</t>
         </is>
       </c>
     </row>
@@ -6221,12 +6221,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>임진영</t>
+          <t>함재원</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>125</t>
         </is>
       </c>
     </row>
@@ -6238,12 +6238,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>송강민</t>
+          <t>이동후</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>393</t>
         </is>
       </c>
     </row>
@@ -6272,12 +6272,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>이서준</t>
+          <t>이지안</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>129</t>
         </is>
       </c>
     </row>
@@ -6289,12 +6289,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>윤승후</t>
+          <t>이해온</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>217</t>
         </is>
       </c>
     </row>
@@ -6306,12 +6306,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>조문기</t>
+          <t>장지욱</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>380</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>이상현</t>
+          <t>이지원B</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>189</t>
         </is>
       </c>
     </row>
@@ -6340,12 +6340,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>김경원</t>
+          <t>김도연</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>114</t>
         </is>
       </c>
     </row>
@@ -6357,12 +6357,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>서승원</t>
+          <t>이서진</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>210</t>
         </is>
       </c>
     </row>
@@ -6374,12 +6374,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>양성원</t>
+          <t>이서하</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>211</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>강지호</t>
+          <t>김서진</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>350</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>박창서</t>
+          <t>차하린</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>209</t>
         </is>
       </c>
     </row>
@@ -6442,12 +6442,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>김지환</t>
+          <t>김향지</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>170</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>양태웅</t>
+          <t>이예원</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>212</t>
         </is>
       </c>
     </row>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>조윤익</t>
+          <t>전율리</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>193</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>이승훈</t>
+          <t>이재원</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>348</t>
         </is>
       </c>
     </row>
@@ -6544,12 +6544,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>김성주</t>
+          <t>김준영</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>335</t>
         </is>
       </c>
     </row>
@@ -6561,12 +6561,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>김언약</t>
+          <t>김은서</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>179</t>
         </is>
       </c>
     </row>
@@ -6578,12 +6578,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>이석민</t>
+          <t>이희원</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>214</t>
         </is>
       </c>
     </row>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>이윤석</t>
+          <t>이채원</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>136</t>
         </is>
       </c>
     </row>
@@ -6612,12 +6612,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>차재웅</t>
+          <t>최은혁</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>319</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6629,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>송지호</t>
+          <t>양태웅</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>316</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>윤장원</t>
+          <t>이도하</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>214</t>
         </is>
       </c>
     </row>
@@ -6663,12 +6663,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>김동혁</t>
+          <t>김도경</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>390</t>
         </is>
       </c>
     </row>
@@ -6680,12 +6680,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>최현태</t>
+          <t>함하율</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>321</t>
         </is>
       </c>
     </row>
@@ -6697,12 +6697,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>신윤호</t>
+          <t>이승훈</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>375</t>
         </is>
       </c>
     </row>
@@ -6714,12 +6714,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>정재훈</t>
+          <t>임동규</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>395</t>
         </is>
       </c>
     </row>
@@ -6731,12 +6731,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>여인하</t>
+          <t>신지우</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>177</t>
         </is>
       </c>
     </row>
@@ -6748,12 +6748,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>주수빈</t>
+          <t>이지수</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>320</t>
         </is>
       </c>
     </row>
@@ -6765,12 +6765,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>서준혁</t>
+          <t>유태헌</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>392</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>김영도</t>
+          <t>김효빈</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>122</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>김주현</t>
+          <t>김연서</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>167</t>
         </is>
       </c>
     </row>
@@ -6816,12 +6816,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>강기훈</t>
+          <t>구본윤</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>311</t>
         </is>
       </c>
     </row>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>윤태영</t>
+          <t>유지민</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>195</t>
         </is>
       </c>
     </row>
@@ -6850,12 +6850,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>김민서</t>
+          <t>김아빈</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>182</t>
         </is>
       </c>
     </row>
@@ -6867,12 +6867,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>김유빈</t>
+          <t>민봄</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>이재정</t>
+          <t>장지우</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>335</t>
         </is>
       </c>
     </row>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>위원빈</t>
+          <t>신서빈</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>208</t>
         </is>
       </c>
     </row>
@@ -6935,12 +6935,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>유준서</t>
+          <t>이선주</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>203</t>
         </is>
       </c>
     </row>
@@ -6952,12 +6952,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>김상우</t>
+          <t>김우일</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>310</t>
         </is>
       </c>
     </row>
@@ -6969,12 +6969,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>이준우</t>
+          <t>이재정</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>402</t>
         </is>
       </c>
     </row>
@@ -7003,12 +7003,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>조준성</t>
+          <t>조정연</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>199</t>
         </is>
       </c>
     </row>
@@ -7020,12 +7020,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>차지석</t>
+          <t>최재우</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>320</t>
         </is>
       </c>
     </row>
@@ -7037,12 +7037,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>노기완</t>
+          <t>박정언</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>393</t>
         </is>
       </c>
     </row>
@@ -7054,12 +7054,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>김승겸</t>
+          <t>김재윤</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>348</t>
         </is>
       </c>
     </row>
@@ -7071,12 +7071,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>홍동기</t>
+          <t>황서연</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>218</t>
         </is>
       </c>
     </row>
@@ -7088,12 +7088,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>박은찬</t>
+          <t>안선준</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>397</t>
         </is>
       </c>
     </row>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>박재성</t>
+          <t>배기원</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>342</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>최재호</t>
+          <t>최유선</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>152</t>
         </is>
       </c>
     </row>
@@ -7139,12 +7139,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>기정훈</t>
+          <t>김강윤</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>332</t>
         </is>
       </c>
     </row>
@@ -7156,12 +7156,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>이은호</t>
+          <t>전하윤</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>146</t>
         </is>
       </c>
     </row>
@@ -7190,12 +7190,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>김준희</t>
+          <t>김철현</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>374</t>
         </is>
       </c>
     </row>
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>김건우</t>
+          <t>김규린</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>186</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>이연재</t>
+          <t>이승민</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>331</t>
         </is>
       </c>
     </row>
@@ -7241,12 +7241,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>박재윤</t>
+          <t>노희원</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>137</t>
         </is>
       </c>
     </row>
@@ -7258,12 +7258,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>주지환</t>
+          <t>주수빈</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>401</t>
         </is>
       </c>
     </row>
@@ -7275,12 +7275,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>안선준</t>
+          <t>윤정원</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>162</t>
         </is>
       </c>
     </row>
@@ -7292,12 +7292,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>이승훈</t>
+          <t>임강현</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>388</t>
         </is>
       </c>
     </row>
@@ -7309,12 +7309,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>정희도</t>
+          <t>형태은</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>211</t>
         </is>
       </c>
     </row>
@@ -7343,12 +7343,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>배정훈</t>
+          <t>박상혁</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>352</t>
         </is>
       </c>
     </row>
@@ -7360,12 +7360,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>유재현</t>
+          <t>유은아</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>181</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>김서진</t>
+          <t>김용원</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>340</t>
         </is>
       </c>
     </row>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>이서준B</t>
+          <t>정예원</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>130</t>
         </is>
       </c>
     </row>
@@ -7411,12 +7411,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>김민준</t>
+          <t>강지훈</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>368</t>
         </is>
       </c>
     </row>
@@ -7428,12 +7428,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>김민성</t>
+          <t>권현서</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>376</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>김시영</t>
+          <t>김민준</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>378</t>
         </is>
       </c>
     </row>
@@ -7462,12 +7462,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>윤서진</t>
+          <t>유재현</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>359</t>
         </is>
       </c>
     </row>
@@ -7479,12 +7479,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>김경범</t>
+          <t>김나영</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>126</t>
         </is>
       </c>
     </row>
@@ -7496,12 +7496,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>송민종</t>
+          <t>신정욱</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>336</t>
         </is>
       </c>
     </row>
@@ -7513,12 +7513,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>우혁주</t>
+          <t>엄지은</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>150</t>
         </is>
       </c>
     </row>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>박시원</t>
+          <t>문혜찬</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>296</t>
         </is>
       </c>
     </row>
@@ -7547,12 +7547,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>김준희</t>
+          <t>박루민</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>380</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>임강현</t>
+          <t>이채연</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>212</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>심지호</t>
+          <t>송가은</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>230</t>
         </is>
       </c>
     </row>
@@ -7598,12 +7598,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>정대현</t>
+          <t>서지우</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -7615,12 +7615,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>배기원</t>
+          <t>심서현</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>177</t>
         </is>
       </c>
     </row>
@@ -7632,12 +7632,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>송민재</t>
+          <t>민예빈</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>176</t>
         </is>
       </c>
     </row>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>김지혁</t>
+          <t>위원빈</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>379</t>
         </is>
       </c>
     </row>
@@ -7666,12 +7666,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>조민준</t>
+          <t>전하린</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>206</t>
         </is>
       </c>
     </row>
@@ -7683,12 +7683,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>조한율</t>
+          <t>주서현</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>130</t>
         </is>
       </c>
     </row>
@@ -7700,12 +7700,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>이승민</t>
+          <t>박예도</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>368</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>한강인</t>
+          <t>홍지영</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>175</t>
         </is>
       </c>
     </row>
@@ -7734,12 +7734,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>채윤우</t>
+          <t>정은찬</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>396</t>
         </is>
       </c>
     </row>
@@ -7751,12 +7751,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>양인서</t>
+          <t>윤서진</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>352</t>
         </is>
       </c>
     </row>
@@ -7768,12 +7768,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>김동욱</t>
+          <t>김보민</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>221</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>이강민</t>
+          <t>윤담희</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>125</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>박정언</t>
+          <t>양성원</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>김용원</t>
+          <t>김재윤</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>223</t>
         </is>
       </c>
     </row>
@@ -7836,12 +7836,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>정인성</t>
+          <t>오영웅</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>309</t>
         </is>
       </c>
     </row>
@@ -7853,12 +7853,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>류민서</t>
+          <t>유일서</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>173</t>
         </is>
       </c>
     </row>
@@ -7870,12 +7870,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>박지안</t>
+          <t>박민서</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>226</t>
         </is>
       </c>
     </row>
@@ -7887,12 +7887,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>김원준</t>
+          <t>문지현</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>165</t>
         </is>
       </c>
     </row>
@@ -7904,12 +7904,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>김도윤</t>
+          <t>김준영</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>331</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>박찬영</t>
+          <t>박선우</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>227</t>
         </is>
       </c>
     </row>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>김대윤</t>
+          <t>김수민</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>184</t>
         </is>
       </c>
     </row>
@@ -7955,12 +7955,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>김현우</t>
+          <t>박서현</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>207</t>
         </is>
       </c>
     </row>
@@ -7972,12 +7972,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>장하현</t>
+          <t>임하윤</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>233</t>
         </is>
       </c>
     </row>
@@ -7989,12 +7989,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>박현서</t>
+          <t>윤은빈</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>226</t>
         </is>
       </c>
     </row>
@@ -8006,12 +8006,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>김윤후</t>
+          <t>곽환준</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>333</t>
         </is>
       </c>
     </row>
@@ -8023,12 +8023,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>백주영</t>
+          <t>김민서</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>326</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>최해민</t>
+          <t>조민건</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>305</t>
         </is>
       </c>
     </row>
@@ -8057,12 +8057,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>김정현</t>
+          <t>박신후</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>327</t>
         </is>
       </c>
     </row>
@@ -8074,12 +8074,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>김유찬</t>
+          <t>김나연</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>138</t>
         </is>
       </c>
     </row>
@@ -8091,12 +8091,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>권민석</t>
+          <t>김정훈</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>346</t>
         </is>
       </c>
     </row>
@@ -8108,12 +8108,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>김도현</t>
+          <t>김승수</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>342</t>
         </is>
       </c>
     </row>
@@ -8142,12 +8142,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>김익환</t>
+          <t>김시훈</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>404</t>
         </is>
       </c>
     </row>
@@ -8159,12 +8159,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>김재윤</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>157</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>김정훈</t>
+          <t>나하연</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>116</t>
         </is>
       </c>
     </row>
@@ -8193,12 +8193,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>박신후</t>
+          <t>박찬영</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>339</t>
         </is>
       </c>
     </row>
@@ -8210,12 +8210,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>박서율</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>114</t>
         </is>
       </c>
     </row>
@@ -8227,12 +8227,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>구본준</t>
+          <t>김도윤</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>387</t>
         </is>
       </c>
     </row>
@@ -8244,12 +8244,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>윤지호</t>
+          <t>이가현</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>127</t>
         </is>
       </c>
     </row>
@@ -8278,12 +8278,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>엄창통</t>
+          <t>윤하온</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>121</t>
         </is>
       </c>
     </row>
@@ -8295,12 +8295,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>김주영</t>
+          <t>김채현</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>185</t>
         </is>
       </c>
     </row>
@@ -8312,12 +8312,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>임우석</t>
+          <t>전혜린</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>128</t>
         </is>
       </c>
     </row>
@@ -8329,12 +8329,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>김태환</t>
+          <t>박지안</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>390</t>
         </is>
       </c>
     </row>
@@ -8346,12 +8346,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>정도영</t>
+          <t>조형준</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>332</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>김민준</t>
+          <t>권준현</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>343</t>
         </is>
       </c>
     </row>
@@ -8380,12 +8380,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>김도경</t>
+          <t>김유빈</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>381</t>
         </is>
       </c>
     </row>
@@ -8414,12 +8414,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>이민찬</t>
+          <t>이승채</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>202</t>
         </is>
       </c>
     </row>
@@ -8431,12 +8431,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>이준호</t>
+          <t>박채은B</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>191</t>
         </is>
       </c>
     </row>
@@ -8448,12 +8448,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>이서준A</t>
+          <t>이석민</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>347</t>
         </is>
       </c>
     </row>
@@ -8465,12 +8465,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>이도헌</t>
+          <t>이준호</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>359</t>
         </is>
       </c>
     </row>
@@ -8482,12 +8482,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>이준호</t>
+          <t>우지원</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>151</t>
         </is>
       </c>
     </row>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>이창휘</t>
+          <t>최다인</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>170</t>
         </is>
       </c>
     </row>
@@ -8516,12 +8516,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>최예훈</t>
+          <t>주백하</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>364</t>
         </is>
       </c>
     </row>
@@ -8533,12 +8533,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>박주혁</t>
+          <t>유시연</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>117</t>
         </is>
       </c>
     </row>
@@ -8550,12 +8550,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>박지호</t>
+          <t>엄수빈</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>124</t>
         </is>
       </c>
     </row>
@@ -8567,12 +8567,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>이호건</t>
+          <t>주진하</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>229</t>
         </is>
       </c>
     </row>
@@ -8584,12 +8584,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>김형준</t>
+          <t>박재윤</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>326</t>
         </is>
       </c>
     </row>
@@ -8601,12 +8601,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>심정원</t>
+          <t>김현규</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>389</t>
         </is>
       </c>
     </row>
@@ -8618,12 +8618,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>조준민</t>
+          <t>조민준</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>317</t>
         </is>
       </c>
     </row>
@@ -8635,12 +8635,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>유태헌</t>
+          <t>이영진</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>399</t>
         </is>
       </c>
     </row>
@@ -8652,12 +8652,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>이창현</t>
+          <t>차재웅</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>364</t>
         </is>
       </c>
     </row>
@@ -8669,12 +8669,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>윤태환</t>
+          <t>유지민</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>410</t>
         </is>
       </c>
     </row>
@@ -8686,12 +8686,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>김세민</t>
+          <t>김윤아</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>222</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>이재인</t>
+          <t>이진율</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>366</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>천정환</t>
+          <t>장지후</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>223</t>
         </is>
       </c>
     </row>
@@ -8754,12 +8754,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>황윤우</t>
+          <t>한동빈</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>369</t>
         </is>
       </c>
     </row>
@@ -8771,12 +8771,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>이지훈</t>
+          <t>임서준</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>378</t>
         </is>
       </c>
     </row>
@@ -8788,12 +8788,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>변우진</t>
+          <t>박세진</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>297</t>
         </is>
       </c>
     </row>
@@ -8805,12 +8805,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>이영진</t>
+          <t>전지은</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>231</t>
         </is>
       </c>
     </row>
@@ -8839,12 +8839,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>이승원</t>
+          <t>여이솔</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>300</t>
         </is>
       </c>
     </row>
@@ -8856,12 +8856,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>최승호</t>
+          <t>조준민</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>398</t>
         </is>
       </c>
     </row>
@@ -8873,12 +8873,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>남궁우겸</t>
+          <t>송민재</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>376</t>
         </is>
       </c>
     </row>
@@ -8890,12 +8890,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>정찬우</t>
+          <t>최민강</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>406</t>
         </is>
       </c>
     </row>
@@ -8907,12 +8907,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>박예도</t>
+          <t>류건희</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>403</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>유지민</t>
+          <t>임동우</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>298</t>
         </is>
       </c>
     </row>
@@ -8941,12 +8941,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>서지우</t>
+          <t>방지예</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>116</t>
         </is>
       </c>
     </row>
@@ -8958,12 +8958,12 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>이서진</t>
+          <t>이지우A</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>121</t>
         </is>
       </c>
     </row>
@@ -8975,12 +8975,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>김학수</t>
+          <t>권은성</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>364</t>
         </is>
       </c>
     </row>
@@ -8992,12 +8992,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>장윤우</t>
+          <t>정연수</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>130</t>
         </is>
       </c>
     </row>
@@ -9009,12 +9009,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>김동현</t>
+          <t>김용호</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>370</t>
         </is>
       </c>
     </row>
@@ -9026,12 +9026,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>임성주</t>
+          <t>천정환</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>371</t>
         </is>
       </c>
     </row>
@@ -9043,12 +9043,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>최우진</t>
+          <t>허찬범</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>310</t>
         </is>
       </c>
     </row>
@@ -9060,12 +9060,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>이진표</t>
+          <t>이창현</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>340</t>
         </is>
       </c>
     </row>
@@ -9077,12 +9077,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>고현준</t>
+          <t>길현서</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>175</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>김동주</t>
+          <t>강현우</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>347</t>
         </is>
       </c>
     </row>
@@ -9111,12 +9111,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>김경호</t>
+          <t>강수민</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>141</t>
         </is>
       </c>
     </row>
@@ -9128,12 +9128,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>김철현</t>
+          <t>유채연</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>134</t>
         </is>
       </c>
     </row>
@@ -9145,12 +9145,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>김유담</t>
+          <t>김혜연</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>117</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>김범석</t>
+          <t>김다현</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>142</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>김시훈</t>
+          <t>박규민</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>232</t>
         </is>
       </c>
     </row>
@@ -9196,12 +9196,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>안준성</t>
+          <t>서주은</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>196</t>
         </is>
       </c>
     </row>
@@ -9213,12 +9213,12 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>김준영</t>
+          <t>신지윤</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>161</t>
         </is>
       </c>
     </row>
@@ -9230,12 +9230,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>이관후</t>
+          <t>이민찬</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>399</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>조현승</t>
+          <t>장예준</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>358</t>
         </is>
       </c>
     </row>
@@ -9281,12 +9281,12 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>이찬우</t>
+          <t>이혜성</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>181</t>
         </is>
       </c>
     </row>
@@ -9298,12 +9298,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>최주영</t>
+          <t>하선우</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>365</t>
         </is>
       </c>
     </row>
@@ -9332,12 +9332,12 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>강재혁</t>
+          <t>구승규</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>341</t>
         </is>
       </c>
     </row>
@@ -9349,12 +9349,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>최현석</t>
+          <t>허서준</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>366</t>
         </is>
       </c>
     </row>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>권은성</t>
+          <t>김건우</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>308</t>
         </is>
       </c>
     </row>
@@ -9383,12 +9383,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>이해준</t>
+          <t>조수진</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>176</t>
         </is>
       </c>
     </row>
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>허제</t>
+          <t>홍예주</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>173</t>
         </is>
       </c>
     </row>
@@ -9417,12 +9417,12 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>정윤상</t>
+          <t>정현지</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>154</t>
         </is>
       </c>
     </row>
@@ -9434,12 +9434,12 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>신현수</t>
+          <t>이서연</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>183</t>
         </is>
       </c>
     </row>
@@ -9508,6 +9508,295 @@
       <c r="C535" t="inlineStr">
         <is>
           <t>282</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>20613</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>여은수</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>20205</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>문민서</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>20301</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>권민석</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>20417</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>이상현</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>20504</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>김범석</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>30131</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>홍준서</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>20607</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>변우진</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>20103</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>김동욱</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>박시윤</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>10328</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>황예진</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>10408</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>노규민</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>10428</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>차하윤</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>김태우</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>10620</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>이재혁</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>10127</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>최재율</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>10214</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>서정욱</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>구자영</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>401</t>
         </is>
       </c>
     </row>

--- a/students.xlsx
+++ b/students.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C552"/>
+  <dimension ref="A1:C554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>336</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>311</t>
         </is>
       </c>
     </row>
@@ -480,7 +480,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>329</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>301</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>290</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>337</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>321</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>189</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>147</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>159</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>354</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>288</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>280</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>288</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>284</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>316</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>165</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>188</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>217</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>153</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>197</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>157</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>123</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>139</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>377</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>160</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>139</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>193</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>392</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>276</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>291</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>240</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>315</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>327</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>302</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>344</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>383</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>125</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>290</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>276</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>146</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>386</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>155</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>297</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>293</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>162</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>152</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>409</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>300</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>214</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>231</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>169</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>410</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>144</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>407</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>141</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>334</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>336</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>134</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>176</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>370</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>331</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>220</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>151</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>320</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>139</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>406</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>127</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>359</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>167</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>172</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>172</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>113</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>306</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>279</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>195</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>192</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>281</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>170</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>333</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>159</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>360</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>272</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>186</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>191</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>380</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>298</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>405</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>358</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>168</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>281</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>325</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>186</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>122</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>295</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>327</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>382</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>294</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>385</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>230</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>309</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>277</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>145</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>297</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>241</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>348</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>280</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>390</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>221</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>394</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>156</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>371</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>193</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>198</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>322</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>144</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>317</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>235</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>369</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>187</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>301</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>240</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>283</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>197</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>209</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>376</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>182</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>362</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>121</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>289</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>154</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>237</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>234</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>289</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>170</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>355</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>201</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>363</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>273</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>182</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>199</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>312</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>203</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>360</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>299</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>237</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>196</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>150</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>218</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>341</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>219</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>343</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>299</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>178</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>214</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>174</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>206</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>128</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>346</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>135</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>347</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>293</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>214</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>368</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>357</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>218</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>194</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>157</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>358</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>125</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>223</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>138</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>364</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>368</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>239</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>330</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>220</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>121</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>373</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>278</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>377</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>287</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>222</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>166</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>133</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>215</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>173</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>164</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>116</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>226</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>198</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>328</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>323</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>131</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>196</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>133</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>365</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>171</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>195</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>122</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>285</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>124</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>121</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>300</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>174</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>223</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>213</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>187</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>177</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>388</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>135</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>367</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>352</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>202</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>326</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>389</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>219</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>230</t>
         </is>
       </c>
     </row>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>362</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>370</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>177</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>215</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>239</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>316</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>151</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>225</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>222</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>395</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>154</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>309</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>166</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>148</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>397</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>154</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>378</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>207</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>312</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>196</t>
         </is>
       </c>
     </row>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>186</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>313</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>170</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>175</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>298</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>232</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>339</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>223</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>303</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>284</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>241</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>272</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>211</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>232</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>321</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>182</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>212</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>155</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>279</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>326</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>299</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5342,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>273</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>160</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>296</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>384</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>158</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>183</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>387</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>311</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>193</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>136</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>181</t>
         </is>
       </c>
     </row>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>140</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>396</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>169</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>137</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>318</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>329</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>319</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>352</t>
         </is>
       </c>
     </row>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>301</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>356</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>334</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>138</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>296</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>310</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>197</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>299</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>312</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>182</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>204</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>114</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>193</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>345</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>120</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>216</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>175</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>225</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>349</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6090,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>277</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>190</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>310</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>168</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>210</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>120</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>217</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>319</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>130</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>361</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>188</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>189</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>314</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>224</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>129</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>234</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>235</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>361</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>228</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>164</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>236</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>184</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>317</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>332</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>131</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>238</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>238</t>
         </is>
       </c>
     </row>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>374</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>409</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>158</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>295</t>
         </is>
       </c>
     </row>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>376</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>307</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>363</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>113</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>321</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>372</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>129</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>187</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>366</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>174</t>
         </is>
       </c>
     </row>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>191</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6872,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>231</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>293</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>165</t>
         </is>
       </c>
     </row>
@@ -6918,12 +6918,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>이준익</t>
+          <t>김예승</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>351</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>158</t>
         </is>
       </c>
     </row>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>276</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>324</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>142</t>
         </is>
       </c>
     </row>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>375</t>
         </is>
       </c>
     </row>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>371</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>323</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>141</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>333</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>307</t>
         </is>
       </c>
     </row>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>185</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>338</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>126</t>
         </is>
       </c>
     </row>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>379</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>224</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>290</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>205</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>168</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>285</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -7326,12 +7326,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>진승현</t>
+          <t>최서윤</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>342</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>208</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>305</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>233</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>291</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>353</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>354</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>272</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>117</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>297</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>161</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>356</t>
         </is>
       </c>
     </row>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>229</t>
         </is>
       </c>
     </row>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>320</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>221</t>
         </is>
       </c>
     </row>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>143</t>
         </is>
       </c>
     </row>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>227</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>173</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>353</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>132</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>364</t>
         </is>
       </c>
     </row>
@@ -7756,7 +7756,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>375</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>135</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>162</t>
         </is>
       </c>
     </row>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>338</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>355</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>153</t>
         </is>
       </c>
     </row>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>184</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>192</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>286</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>185</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>127</t>
         </is>
       </c>
     </row>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>143</t>
         </is>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>178</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>159</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>374</t>
         </is>
       </c>
     </row>
@@ -8028,7 +8028,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>292</t>
         </is>
       </c>
     </row>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>287</t>
         </is>
       </c>
     </row>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>298</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>116</t>
         </is>
       </c>
     </row>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>284</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>331</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>328</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>117</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>132</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>411</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>128</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>286</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>134</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>125</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>152</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>140</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>335</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>366</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>393</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8385,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>406</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>179</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>314</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>282</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>155</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>128</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>271</t>
         </is>
       </c>
     </row>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>124</t>
         </is>
       </c>
     </row>
@@ -8555,7 +8555,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>233</t>
         </is>
       </c>
     </row>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>408</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>313</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>372</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>303</t>
         </is>
       </c>
     </row>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>308</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>369</t>
         </is>
       </c>
     </row>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>138</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>283</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>156</t>
         </is>
       </c>
     </row>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>305</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>308</t>
         </is>
       </c>
     </row>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>330</t>
         </is>
       </c>
     </row>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>195</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>278</t>
         </is>
       </c>
     </row>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>325</t>
         </is>
       </c>
     </row>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>274</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>277</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>381</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>410</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>131</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>189</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>367</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>137</t>
         </is>
       </c>
     </row>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>373</t>
         </is>
       </c>
     </row>
@@ -9048,7 +9048,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>391</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>310</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>121</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>335</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>146</t>
         </is>
       </c>
     </row>
@@ -9133,7 +9133,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>236</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>176</t>
         </is>
       </c>
     </row>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>147</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>164</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>145</t>
         </is>
       </c>
     </row>
@@ -9235,7 +9235,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>400</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>216</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9303,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>366</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>275</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>332</t>
         </is>
       </c>
     </row>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>273</t>
         </is>
       </c>
     </row>
@@ -9388,7 +9388,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>171</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>141</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>179</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>김원중</t>
+          <t>남강민</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>322</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>179</t>
         </is>
       </c>
     </row>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>116</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>289</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>357</t>
         </is>
       </c>
     </row>
@@ -9626,7 +9626,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>337</t>
         </is>
       </c>
     </row>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>405</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>232</t>
         </is>
       </c>
     </row>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>142</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>340</t>
         </is>
       </c>
     </row>
@@ -9745,7 +9745,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>398</t>
         </is>
       </c>
     </row>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>350</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>359</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9796,41 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>379</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>10329</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>유제인</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>김지온</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>229</t>
         </is>
       </c>
     </row>
